--- a/光伏配储项目/电价数据/2026/漳港站.xlsx
+++ b/光伏配储项目/电价数据/2026/漳港站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50901</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74311</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57224</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49598</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27229</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11625</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09461</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10306</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08762</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11305</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03609</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09581999999999999</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09679</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06620000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08989</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03874</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01997</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14224</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21262</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22063</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.22075</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21168</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.05588</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00954</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.22608</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11943</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52763</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.7129500000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59717</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42061</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5702699999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6040399999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79139</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6396799999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.60846</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73446</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.87663</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66107</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58578</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.67103</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62325</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60046</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48051</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6888200000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.14087</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6665599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.71492</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5018</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50471</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50447</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48698</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.56837</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.54683</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.16819</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.08669</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9556699999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.67401</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.20572</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5965900000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66828</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6541</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7143200000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.4287</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7560800000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.47821</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50819</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42776</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20978</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22775</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21025</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.1773</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.59284</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.19557</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45695</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.49058</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6038300000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47244</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4372799999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23972</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.17279</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26658</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.17096</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56598</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.08796</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.08927</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.09986</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.21804</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.22509</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6454500000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.09376000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.20048</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.17066</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.52008</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30148</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.06898</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.06903000000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.06695999999999999</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.07887999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.07968</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02697</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.00408</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.00818</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.01235</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.00737</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03683</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03904999999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03901</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08425000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05915</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00372</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.17038</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02939</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09225</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46783</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35127</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65507</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44796</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.07204000000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.02701</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01408</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0349</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03781</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.01021</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.01224</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14269</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33556</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3171</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9139299999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86213</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29576</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8867200000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6314500000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18631</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8683500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33006</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03236</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7903300000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5316000000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7723099999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7770199999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766900000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87352</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49253</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39908</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20619</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87879</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62105</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53812</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49745</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45571</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5873400000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59633</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60302</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69445</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46796</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58189</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88303</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8466900000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82431</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86168</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44181</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26369</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35372</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9189400000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46679</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50175</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16441</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19335</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59951</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8910399999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3758</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16533</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70096</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79195</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66823</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58457</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50181</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43897</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43516</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45255</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43601</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49561</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5434</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27061</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57117</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8664700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46651</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3244</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22125</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13768</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15084</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13511</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14081</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13392</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13418</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13304</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09345000000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10548</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11759</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13284</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13724</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34917</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5406799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19555</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3607</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43821</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.09941</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.10835</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6891499999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50805</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21957</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2953</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.53426</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.52638</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.5182599999999999</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.52525</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.5194500000000001</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.6278899999999999</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.4973399999999999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34997</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565599999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7769299999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45958</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34491</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19822</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21459</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27623</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.16848</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.73094</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.68669</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.69859</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5826699999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.92403</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49403</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.91272</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5737100000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5418500000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.46294</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3606</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52925</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42058</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5655399999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50447</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5224099999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6271599999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.20516</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49451</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.59282</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.78846</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6349900000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.78418</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.07779</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.72909</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8128300000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58587</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5267200000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8375499999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76903</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67173</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47257</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48389</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47858</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47102</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55403</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45701</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10754</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18248</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41877</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41157</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36765</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44689</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22887</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22856</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24436</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14307</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16715</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18584</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23604</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3511</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22505</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.006820000000000001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15652</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01491</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02425</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02998</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.00634</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02968</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01368</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03434</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48147</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.39868</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.97234</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.93757</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.46956</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.55231</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.43838</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.46233</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9860399999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.06227</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.93614</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.96912</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.17598</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.16454</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25405</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3238</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.24657</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49619</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.47906</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14053</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33004</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45566</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44883</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57728</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23942</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36856</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47802</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49553</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57256</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.57345</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.63122</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49565</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47418</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.61861</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7481</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7042999999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.60248</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53371</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37275</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14394</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20345</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15496</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14749</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05715</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04488</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06791</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18639</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07281</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05533</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.21947</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15958</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19157</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38685</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06353</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39728</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57516</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46472</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.16171</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.03892</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04765</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.07859000000000001</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.08177</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02455</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.17855</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.07697</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.20753</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36986</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18483</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15424</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21113</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12578</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23815</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.05925</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.06247</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.06231</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.07260999999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.05411999999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.09565</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24165</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16365</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.08774</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21206</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15282</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39702</v>
       </c>
     </row>
   </sheetData>
